--- a/Week06-Mobile-Testing/Day07-FaceLab-Exploratory-Testing/FaceLab-TestCases.xlsx
+++ b/Week06-Mobile-Testing/Day07-FaceLab-Exploratory-Testing/FaceLab-TestCases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/cf62e5d164005fe0/Belgeler/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="73" documentId="8_{0625E5BD-1C15-451E-9828-A462B4A981BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{894EBA9D-DADD-40B8-BF63-F3F6C4E626E1}"/>
+  <xr:revisionPtr revIDLastSave="101" documentId="8_{0625E5BD-1C15-451E-9828-A462B4A981BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E918DA4-E8DA-48DF-9F3A-B91C4589CD0C}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C612A6CB-63D8-47E1-BF09-31A7049604DD}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="48">
   <si>
     <t>ID</t>
   </si>
@@ -93,14 +93,6 @@
     <t>Verify user can select photo from gallery</t>
   </si>
   <si>
-    <t>Photo library permisson granted</t>
-  </si>
-  <si>
-    <t>1. Open Face Studio
-2. Tap Album
-3. Select a photo</t>
-  </si>
-  <si>
     <t>Selected photo should be open in editing screen</t>
   </si>
   <si>
@@ -110,19 +102,7 @@
     <t>TC-03</t>
   </si>
   <si>
-    <t>Verify camera permisson request appears</t>
-  </si>
-  <si>
-    <t>Camera permisson not granted</t>
-  </si>
-  <si>
-    <t>1. Tap Camera in Face Studio</t>
-  </si>
-  <si>
     <t>System photo should display camera permisson dialog</t>
-  </si>
-  <si>
-    <t>Camera permisson dialog displayed</t>
   </si>
   <si>
     <t>TC-04</t>
@@ -169,7 +149,48 @@
     <t>iOS</t>
   </si>
   <si>
-    <t>FaceLab does not open. Photo remains in gallery. Not: Works correctly on Android - platform inconsistency</t>
+    <t>1. Open FaceLab
+2. Tap Album
+3. Select a photo</t>
+  </si>
+  <si>
+    <t>1. Tap Camera in FaceLab</t>
+  </si>
+  <si>
+    <t>FaceLab does not open. Photo remains in gallery. 
+Not: Works correctly on Android - platform inconsistency</t>
+  </si>
+  <si>
+    <t>TC-06</t>
+  </si>
+  <si>
+    <t>Verify warning appears for faceless photo</t>
+  </si>
+  <si>
+    <t>Gallery permission granted</t>
+  </si>
+  <si>
+    <t>1. Open FaceLab
+2. Select a photo without a face
+3. Apply filter</t>
+  </si>
+  <si>
+    <t>Warning message should be displayed</t>
+  </si>
+  <si>
+    <t>Warning message displayed successfully</t>
+  </si>
+  <si>
+    <t>Verify camera permission request appears</t>
+  </si>
+  <si>
+    <t>Photo library permission granted</t>
+  </si>
+  <si>
+    <t>Camera permission not granted</t>
+  </si>
+  <si>
+    <t>Camera permission dialog displayed</t>
   </si>
 </sst>
 </file>
@@ -545,14 +566,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AC63081-F1A8-4A02-BF53-C3B97FA2476D}">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="38.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.42578125" customWidth="1"/>
     <col min="3" max="3" width="30" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15" style="1" customWidth="1"/>
-    <col min="5" max="5" width="50.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="97.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="49.5703125" customWidth="1"/>
+    <col min="6" max="6" width="52" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.42578125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -572,7 +594,7 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="G1" t="s">
@@ -582,7 +604,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="135" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -598,7 +620,7 @@
       <c r="E2" t="s">
         <v>12</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G2" t="s">
@@ -608,7 +630,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="105" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -616,16 +638,16 @@
         <v>17</v>
       </c>
       <c r="C3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="E3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" t="s">
-        <v>21</v>
       </c>
       <c r="G3" t="s">
         <v>14</v>
@@ -634,50 +656,50 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="E4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F4" t="s">
-        <v>27</v>
+        <v>21</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="G4" t="s">
         <v>14</v>
       </c>
       <c r="H4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="E5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F5" t="s">
-        <v>33</v>
+        <v>26</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="G5" t="s">
         <v>14</v>
@@ -686,30 +708,56 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="135" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C6" t="s">
         <v>10</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E6" t="s">
+      <c r="G6" t="s">
+        <v>33</v>
+      </c>
+      <c r="H6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>38</v>
       </c>
-      <c r="F6" t="s">
+      <c r="B7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="G6" t="s">
-        <v>39</v>
-      </c>
-      <c r="H6" t="s">
-        <v>40</v>
+      <c r="E7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
